--- a/data/single_run/input/components/distances/coordinates_meisner.xlsx
+++ b/data/single_run/input/components/distances/coordinates_meisner.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -765,486 +765,216 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ccp_10</t>
+          <t>axp_1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>axp_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ccp_11</t>
+          <t>axp_3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>r2_1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ccp_12</t>
+          <t>r2_2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>r2_3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ccp_13</t>
+          <t>r2_4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>r2_5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ccp_14</t>
+          <t>r2_6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>r1_14</t>
+          <t>r2_7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ccp_15</t>
+          <t>r2_8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>r1_15</t>
+          <t>r2_9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Role1</t>
+          <t>Role2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>axp_1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>15</v>
-      </c>
-      <c r="D32" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>axp_2</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>45</v>
-      </c>
-      <c r="D33" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>axp_3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>75</v>
-      </c>
-      <c r="D34" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>r2_1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D35" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>r2_2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D36" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>r2_3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="D37" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>r2_4</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="D38" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>r2_5</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="D39" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>r2_6</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="D40" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>r2_7</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="D41" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>r2_8</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="D42" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>r2_9</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="D43" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>r2_10</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="D44" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>r2_11</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="D45" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>r2_12</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="D46" t="n">
         <v>15</v>
       </c>
     </row>
